--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -16509,16 +16509,16 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O95" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0.4664471010790133</v>
+        <v>0.4701199128985332</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -19177,16 +19177,16 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O111" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>0.5215392783718101</v>
+        <v>0.52521209019133</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -21845,16 +21845,16 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="O127" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="Q127" t="n">
         <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>0.1248756018636729</v>
+        <v>0.1505852846003114</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5485</v>
+        <v>5494</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -20665,16 +20665,16 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O117" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0.5472489611084488</v>
+        <v>0.5509217729279685</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -23333,16 +23333,16 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="O133" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q133" t="n">
         <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>0.1285484136831927</v>
+        <v>0.1469124727807916</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -24351,6 +24351,154 @@
       <c r="BC138" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr"/>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24387,7 +24535,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -24470,7 +24618,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10">
@@ -24480,7 +24628,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -24532,7 +24680,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5501</v>
+        <v>5507</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>129</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1306,9 +1303,6 @@
       <c r="O5" t="n">
         <v>36</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.6403713015110895</v>
       </c>
@@ -1702,9 +1696,6 @@
       <c r="O7" t="n">
         <v>60</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>1.061385495477304</v>
       </c>
@@ -2347,7 +2338,7 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN10" t="b">
@@ -2494,9 +2485,6 @@
       <c r="O11" t="n">
         <v>27</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.2523117715636503</v>
       </c>
@@ -4370,9 +4358,6 @@
       <c r="O23" t="n">
         <v>37</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4763,9 +4748,6 @@
       <c r="O25" t="n">
         <v>29</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.5158546595505998</v>
       </c>
@@ -5159,9 +5141,6 @@
       <c r="O27" t="n">
         <v>45</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.7960391216079779</v>
       </c>
@@ -5804,7 +5783,7 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN30" t="b">
@@ -5951,9 +5930,6 @@
       <c r="O31" t="n">
         <v>23</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.214932249850517</v>
       </c>
@@ -7679,9 +7655,6 @@
       <c r="O42" t="n">
         <v>31</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8072,9 +8045,6 @@
       <c r="O44" t="n">
         <v>31</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.5514308429678827</v>
       </c>
@@ -8468,9 +8438,6 @@
       <c r="O46" t="n">
         <v>30</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.5306927477386518</v>
       </c>
@@ -9113,7 +9080,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -9260,9 +9227,6 @@
       <c r="O50" t="n">
         <v>20</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.1868976085656669</v>
       </c>
@@ -10840,9 +10804,6 @@
       <c r="O60" t="n">
         <v>220</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.8080186002943539</v>
       </c>
@@ -10988,9 +10949,6 @@
       <c r="O61" t="n">
         <v>94</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="S61" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11381,9 +11339,6 @@
       <c r="O63" t="n">
         <v>29</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.5158546595505998</v>
       </c>
@@ -11777,9 +11732,6 @@
       <c r="O65" t="n">
         <v>46</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.8137288798659329</v>
       </c>
@@ -12173,9 +12125,6 @@
       <c r="O67" t="n">
         <v>38</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.7186789772592951</v>
       </c>
@@ -12422,7 +12371,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -12569,9 +12518,6 @@
       <c r="O69" t="n">
         <v>31</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.2896912932767837</v>
       </c>
@@ -14149,9 +14095,6 @@
       <c r="O79" t="n">
         <v>207</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.7602720466405966</v>
       </c>
@@ -14297,9 +14240,6 @@
       <c r="O80" t="n">
         <v>115</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14690,9 +14630,6 @@
       <c r="O82" t="n">
         <v>13</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.2312451922123379</v>
       </c>
@@ -15086,9 +15023,6 @@
       <c r="O84" t="n">
         <v>58</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>1.026005978961394</v>
       </c>
@@ -15482,9 +15416,6 @@
       <c r="O86" t="n">
         <v>40</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.7565041865887316</v>
       </c>
@@ -15731,7 +15662,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -15878,9 +15809,6 @@
       <c r="O88" t="n">
         <v>30</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.2803464128485004</v>
       </c>
@@ -17606,9 +17534,6 @@
       <c r="O99" t="n">
         <v>40</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.01146015253107754</v>
       </c>
@@ -17754,9 +17679,6 @@
       <c r="O100" t="n">
         <v>128</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.4701199128985332</v>
       </c>
@@ -17902,9 +17824,6 @@
       <c r="O101" t="n">
         <v>30</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.5336427512592412</v>
       </c>
@@ -18298,9 +18217,6 @@
       <c r="O103" t="n">
         <v>37</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.6545210555443374</v>
       </c>
@@ -18694,9 +18610,6 @@
       <c r="O105" t="n">
         <v>36</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.6808537679298584</v>
       </c>
@@ -18943,7 +18856,7 @@
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -19090,9 +19003,6 @@
       <c r="O107" t="n">
         <v>44</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.4111747388444672</v>
       </c>
@@ -19486,9 +19396,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -19634,9 +19541,6 @@
       <c r="O110" t="n">
         <v>87</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.02492583175509365</v>
       </c>
@@ -19782,9 +19686,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -19930,9 +19831,6 @@
       <c r="O112" t="n">
         <v>86</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.02463932794181671</v>
       </c>
@@ -20078,9 +19976,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20226,9 +20121,6 @@
       <c r="O114" t="n">
         <v>97</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.02779086988786304</v>
       </c>
@@ -20374,9 +20266,6 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -20522,9 +20411,6 @@
       <c r="O116" t="n">
         <v>101</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.02893688514097079</v>
       </c>
@@ -20670,9 +20556,6 @@
       <c r="O117" t="n">
         <v>150</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.5509217729279685</v>
       </c>
@@ -20818,9 +20701,6 @@
       <c r="O118" t="n">
         <v>37</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.6581593932197309</v>
       </c>
@@ -21214,9 +21094,6 @@
       <c r="O120" t="n">
         <v>41</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.7252800885761576</v>
       </c>
@@ -21610,9 +21487,6 @@
       <c r="O122" t="n">
         <v>63</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.5887274669818509</v>
       </c>
@@ -22006,9 +21880,6 @@
       <c r="O124" t="n">
         <v>0</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0</v>
       </c>
@@ -22154,9 +22025,6 @@
       <c r="O125" t="n">
         <v>91</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.0260718470082014</v>
       </c>
@@ -22302,9 +22170,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -22450,9 +22315,6 @@
       <c r="O127" t="n">
         <v>157</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.04498109868447935</v>
       </c>
@@ -22598,9 +22460,6 @@
       <c r="O128" t="n">
         <v>0</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0</v>
       </c>
@@ -22746,9 +22605,6 @@
       <c r="O129" t="n">
         <v>216</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.06188482366781873</v>
       </c>
@@ -22894,9 +22750,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -23042,9 +22895,6 @@
       <c r="O131" t="n">
         <v>226</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0647498618005881</v>
       </c>
@@ -23190,9 +23040,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -23338,9 +23185,6 @@
       <c r="O133" t="n">
         <v>40</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.1469124727807916</v>
       </c>
@@ -23481,16 +23325,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O134" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="R134" t="n">
-        <v>0.284609467338262</v>
+        <v>0.3379737424641861</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23643,10 +23484,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O135" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -23877,16 +23718,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="O136" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R136" t="n">
-        <v>0.1768975825795506</v>
+        <v>0.5130029894806968</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -24039,10 +23877,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="O137" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -24278,9 +24116,6 @@
       <c r="O138" t="n">
         <v>229</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.06560937324041893</v>
       </c>
@@ -24426,9 +24261,6 @@
       <c r="O139" t="n">
         <v>0</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0</v>
       </c>
@@ -24499,6 +24331,151 @@
       <c r="BC139" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>187</v>
+      </c>
+      <c r="O140" t="n">
+        <v>187</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.0535762130827875</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24535,7 +24512,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -24618,7 +24595,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -24628,7 +24605,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -24680,7 +24657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5507</v>
+        <v>5716</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23325,13 +23325,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O134" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R134" t="n">
-        <v>0.3379737424641861</v>
+        <v>0.426914201007393</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23484,10 +23484,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O135" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5716</v>
+        <v>5721</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23180,13 +23180,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="O133" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="R133" t="n">
-        <v>0.1469124727807916</v>
+        <v>0.2130230855321478</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23325,13 +23325,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="O134" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="R134" t="n">
-        <v>0.426914201007393</v>
+        <v>0.5158546595505998</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -23484,10 +23484,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="O135" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -24657,7 +24657,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5721</v>
+        <v>5744</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -14235,10 +14235,10 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O80" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -14391,10 +14391,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O81" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="U81" t="inlineStr">
         <is>
@@ -17674,13 +17674,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O100" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="R100" t="n">
-        <v>0.4701199128985332</v>
+        <v>0.4737927247180529</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17780,12 +17780,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -17819,22 +17819,19 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O101" t="n">
-        <v>30</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.5336427512592412</v>
+        <v>53</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -17854,12 +17851,12 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -17867,47 +17864,47 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -17939,12 +17936,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -17978,24 +17975,24 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="O102" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V102" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W102" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X102" t="inlineStr">
@@ -18010,7 +18007,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -18025,7 +18022,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD102" t="inlineStr">
@@ -18060,17 +18057,17 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
+          <t>PHO IDTO current-year monthly preliminary cryptosporidiosis notifications; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM102" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN102" t="b">
@@ -18088,12 +18085,12 @@
       </c>
       <c r="AQ102" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1270</t>
+          <t>SER_CA_ON_PHO_IDTO_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
@@ -18101,47 +18098,47 @@
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -18173,12 +18170,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -18212,13 +18209,13 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="O103" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="R103" t="n">
-        <v>0.6545210555443374</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S103" t="inlineStr">
         <is>
@@ -18227,7 +18224,7 @@
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -18247,12 +18244,12 @@
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT103" t="n">
@@ -18260,47 +18257,47 @@
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18332,12 +18329,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -18371,29 +18368,29 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="O104" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V104" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W104" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -18418,7 +18415,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD104" t="inlineStr">
@@ -18453,17 +18450,17 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN104" t="b">
@@ -18481,12 +18478,12 @@
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT104" t="n">
@@ -18494,47 +18491,47 @@
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -18566,12 +18563,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -18605,13 +18602,13 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O105" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="R105" t="n">
-        <v>0.6808537679298584</v>
+        <v>0.6545210555443374</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -18620,7 +18617,7 @@
       </c>
       <c r="U105" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -18645,7 +18642,7 @@
       </c>
       <c r="AS105" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
@@ -18658,42 +18655,42 @@
       </c>
       <c r="AV105" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA105" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB105" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC105" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18725,12 +18722,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -18764,29 +18761,29 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O106" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>Cryptosporidiosis</t>
+          <t>Cryptosporidose</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -18796,7 +18793,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -18811,7 +18808,7 @@
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD106" t="inlineStr">
@@ -18846,17 +18843,17 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN106" t="b">
@@ -18879,7 +18876,7 @@
       </c>
       <c r="AS106" t="inlineStr">
         <is>
-          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
@@ -18892,42 +18889,42 @@
       </c>
       <c r="AV106" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA106" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB106" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC106" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -18959,12 +18956,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -18998,13 +18995,13 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O107" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="R107" t="n">
-        <v>0.4111747388444672</v>
+        <v>0.6808537679298584</v>
       </c>
       <c r="S107" t="inlineStr">
         <is>
@@ -19013,7 +19010,7 @@
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -19038,7 +19035,7 @@
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT107" t="n">
@@ -19051,42 +19048,42 @@
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19118,12 +19115,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -19157,29 +19154,29 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="O108" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W108" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>Cryptosporidiuminfektion</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -19189,7 +19186,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -19204,7 +19201,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr">
@@ -19239,17 +19236,17 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN108" t="b">
@@ -19272,7 +19269,7 @@
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT108" t="n">
@@ -19285,42 +19282,42 @@
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -19352,12 +19349,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -19382,7 +19379,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -19391,81 +19388,95 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="O109" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>0.4111747388444672</v>
       </c>
       <c r="S109" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS109" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ109" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS109" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19492,17 +19503,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -19527,7 +19538,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
@@ -19536,81 +19547,170 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="O110" t="n">
-        <v>87</v>
-      </c>
-      <c r="R110" t="n">
-        <v>0.02492583175509365</v>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>44</v>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X110" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD110" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE110" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG110" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH110" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM110" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN110" t="b">
+        <v>1</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS110" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ110" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS110" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -19672,7 +19772,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -19817,7 +19917,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -19826,13 +19926,13 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O112" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="R112" t="n">
-        <v>0.02463932794181671</v>
+        <v>0.02492583175509365</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -19962,7 +20062,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -20107,7 +20207,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
@@ -20116,13 +20216,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="O114" t="n">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="R114" t="n">
-        <v>0.02779086988786304</v>
+        <v>0.02463932794181671</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -20252,7 +20352,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
@@ -20261,13 +20361,13 @@
         </is>
       </c>
       <c r="N115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S115" t="inlineStr">
         <is>
@@ -20397,7 +20497,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -20406,13 +20506,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O116" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="R116" t="n">
-        <v>0.02893688514097079</v>
+        <v>0.02779086988786304</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -20512,12 +20612,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -20542,22 +20642,22 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N117" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="O117" t="n">
-        <v>150</v>
+        <v>1</v>
       </c>
       <c r="R117" t="n">
-        <v>0.5509217729279685</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S117" t="inlineStr">
         <is>
@@ -20590,42 +20690,42 @@
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -20657,12 +20757,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -20687,104 +20787,90 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N118" t="n">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="O118" t="n">
-        <v>37</v>
+        <v>101</v>
       </c>
       <c r="R118" t="n">
-        <v>0.6581593932197309</v>
+        <v>0.02893688514097079</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA118" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ118" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS118" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR118" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -20811,17 +20897,17 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -20855,170 +20941,81 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="O119" t="n">
-        <v>37</v>
-      </c>
-      <c r="U119" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V119" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X119" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y119" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA119" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD119" t="inlineStr">
+        <v>154</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.5656130202060476</v>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP119" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR119" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS119" t="inlineStr"/>
+      <c r="AT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE119" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF119" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG119" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH119" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM119" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN119" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP119" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ119" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS119" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT119" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV119" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21050,12 +21047,12 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -21089,13 +21086,13 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O120" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="R120" t="n">
-        <v>0.7252800885761576</v>
+        <v>0.6581593932197309</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -21104,7 +21101,7 @@
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -21124,12 +21121,12 @@
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT120" t="n">
@@ -21137,47 +21134,47 @@
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21209,12 +21206,12 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -21248,29 +21245,29 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="O121" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V121" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W121" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y121" t="inlineStr">
@@ -21295,7 +21292,7 @@
       </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD121" t="inlineStr">
@@ -21330,17 +21327,17 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -21358,12 +21355,12 @@
       </c>
       <c r="AQ121" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT121" t="n">
@@ -21371,47 +21368,47 @@
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA121" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB121" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC121" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21443,12 +21440,12 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -21482,13 +21479,13 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="O122" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="R122" t="n">
-        <v>0.5887274669818509</v>
+        <v>0.7252800885761576</v>
       </c>
       <c r="S122" t="inlineStr">
         <is>
@@ -21497,7 +21494,7 @@
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -21522,7 +21519,7 @@
       </c>
       <c r="AS122" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
@@ -21535,42 +21532,42 @@
       </c>
       <c r="AV122" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA122" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB122" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC122" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21602,12 +21599,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -21641,29 +21638,29 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="O123" t="n">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="V123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="W123" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>Cryptosporidiuminfektion</t>
+          <t>Cryptosporidose</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
@@ -21688,7 +21685,7 @@
       </c>
       <c r="AC123" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD123" t="inlineStr">
@@ -21723,17 +21720,17 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -21756,7 +21753,7 @@
       </c>
       <c r="AS123" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
@@ -21769,42 +21766,42 @@
       </c>
       <c r="AV123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA123" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB123" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC123" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21836,12 +21833,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21866,7 +21863,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -21875,81 +21872,95 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>0.5887274669818509</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS124" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ124" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS124" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU124" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -21976,17 +21987,17 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22011,7 +22022,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -22020,81 +22031,170 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="O125" t="n">
-        <v>91</v>
-      </c>
-      <c r="R125" t="n">
-        <v>0.0260718470082014</v>
-      </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD125" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE125" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG125" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH125" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM125" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN125" t="b">
+        <v>1</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS125" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ125" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS125" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU125" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22156,7 +22256,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22301,7 +22401,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22310,13 +22410,13 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="O127" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="R127" t="n">
-        <v>0.04498109868447935</v>
+        <v>0.0260718470082014</v>
       </c>
       <c r="S127" t="inlineStr">
         <is>
@@ -22446,7 +22546,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22591,7 +22691,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22600,13 +22700,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
       <c r="O129" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
       <c r="R129" t="n">
-        <v>0.06188482366781873</v>
+        <v>0.04498109868447935</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22736,7 +22836,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22881,7 +22981,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22890,13 +22990,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O131" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="R131" t="n">
-        <v>0.0647498618005881</v>
+        <v>0.06188482366781873</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -23026,7 +23126,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23141,12 +23241,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -23171,22 +23271,22 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N133" t="n">
-        <v>58</v>
+        <v>226</v>
       </c>
       <c r="O133" t="n">
-        <v>58</v>
+        <v>226</v>
       </c>
       <c r="R133" t="n">
-        <v>0.2130230855321478</v>
+        <v>0.0647498618005881</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23219,42 +23319,42 @@
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23286,12 +23386,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -23316,104 +23416,90 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N134" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="O134" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>0.5158546595505998</v>
+        <v>0</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA134" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ134" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS134" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR134" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23440,17 +23526,17 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23484,170 +23570,81 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="O135" t="n">
-        <v>29</v>
-      </c>
-      <c r="U135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X135" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y135" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA135" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD135" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.2350599564492666</v>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP135" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR135" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS135" t="inlineStr"/>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV135" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE135" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF135" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG135" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM135" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN135" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP135" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ135" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS135" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT135" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV135" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23679,12 +23676,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23724,7 +23721,7 @@
         <v>29</v>
       </c>
       <c r="R136" t="n">
-        <v>0.5130029894806968</v>
+        <v>0.5158546595505998</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23733,7 +23730,7 @@
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -23753,12 +23750,12 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -23766,47 +23763,47 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23838,12 +23835,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23884,22 +23881,22 @@
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -23924,7 +23921,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -23959,17 +23956,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -23987,12 +23984,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -24000,47 +23997,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24072,12 +24069,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24111,81 +24108,95 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>229</v>
+        <v>29</v>
       </c>
       <c r="O138" t="n">
-        <v>229</v>
+        <v>29</v>
       </c>
       <c r="R138" t="n">
-        <v>0.06560937324041893</v>
+        <v>0.5130029894806968</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24212,17 +24223,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24247,7 +24258,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -24256,81 +24267,170 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O139" t="n">
-        <v>0</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>29</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS139" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24392,7 +24492,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
@@ -24401,13 +24501,13 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="O140" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="R140" t="n">
-        <v>0.0535762130827875</v>
+        <v>0.06560937324041893</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -24474,6 +24574,296 @@
         </is>
       </c>
       <c r="BC140" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0</v>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr"/>
+      <c r="AT141" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>187</v>
+      </c>
+      <c r="O142" t="n">
+        <v>187</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.0535762130827875</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr"/>
+      <c r="AT142" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -24595,7 +24985,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10">
@@ -24605,7 +24995,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -24625,7 +25015,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -24657,7 +25047,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5744</v>
+        <v>5811</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -20941,13 +20941,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="O119" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="R119" t="n">
-        <v>0.5656130202060476</v>
+        <v>0.5729586438450872</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23570,13 +23570,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O135" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R135" t="n">
-        <v>0.2350599564492666</v>
+        <v>0.2424055800883061</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23715,13 +23715,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O136" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R136" t="n">
-        <v>0.5158546595505998</v>
+        <v>0.6047951180938068</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23874,10 +23874,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="O137" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -24866,6 +24866,151 @@
       <c r="BC142" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0</v>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
+      <c r="AT143" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24902,7 +25047,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -24985,7 +25130,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10">
@@ -24995,7 +25140,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11">
@@ -25047,7 +25192,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5811</v>
+        <v>5820</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23715,13 +23715,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O136" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R136" t="n">
-        <v>0.6047951180938068</v>
+        <v>0.6581593932197309</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23874,10 +23874,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O137" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5820</v>
+        <v>5823</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -17674,13 +17674,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="O100" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="R100" t="n">
-        <v>0.4737927247180529</v>
+        <v>0.4701199128985332</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -20941,13 +20941,13 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O119" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R119" t="n">
-        <v>0.5729586438450872</v>
+        <v>0.5803042674841269</v>
       </c>
       <c r="S119" t="inlineStr">
         <is>
@@ -23570,13 +23570,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="O135" t="n">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="R135" t="n">
-        <v>0.2424055800883061</v>
+        <v>0.3048433810201426</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23715,13 +23715,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O136" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R136" t="n">
-        <v>0.6581593932197309</v>
+        <v>0.6937355766370136</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23874,10 +23874,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="O137" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -24108,13 +24108,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="O138" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="R138" t="n">
-        <v>0.5130029894806968</v>
+        <v>1.185213803282989</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24267,10 +24267,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="O139" t="n">
-        <v>29</v>
+        <v>67</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -25011,6 +25011,151 @@
       <c r="BC143" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>194</v>
+      </c>
+      <c r="O144" t="n">
+        <v>194</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.05558173977572607</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
+      <c r="AT144" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25047,7 +25192,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -25130,7 +25275,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10">
@@ -25140,7 +25285,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -25192,7 +25337,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5823</v>
+        <v>6075</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23570,13 +23570,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="O135" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="R135" t="n">
-        <v>0.3048433810201426</v>
+        <v>0.3378986873958207</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23715,13 +23715,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O136" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="R136" t="n">
-        <v>0.6937355766370136</v>
+        <v>0.7470998517629377</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23874,10 +23874,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O137" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6075</v>
+        <v>6087</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23570,13 +23570,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O135" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="R135" t="n">
-        <v>0.3378986873958207</v>
+        <v>0.3452443110348603</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23715,13 +23715,13 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O136" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R136" t="n">
-        <v>0.7470998517629377</v>
+        <v>0.8360403103061447</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
@@ -23874,10 +23874,10 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="O137" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6087</v>
+        <v>6094</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23570,13 +23570,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="O135" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="R135" t="n">
-        <v>0.3452443110348603</v>
+        <v>0.3709539937714988</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -25337,7 +25337,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6094</v>
+        <v>6101</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -21833,12 +21833,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -21872,13 +21872,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="O124" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="R124" t="n">
-        <v>0.5887274669818509</v>
+        <v>0.5484655352768304</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -21887,7 +21887,7 @@
       </c>
       <c r="U124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -21912,7 +21912,7 @@
       </c>
       <c r="AS124" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT124" t="n">
@@ -21925,42 +21925,42 @@
       </c>
       <c r="AV124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA124" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB124" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC124" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -21992,12 +21992,12 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -22031,29 +22031,29 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="O125" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>Cryptosporidiuminfektion</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -22063,7 +22063,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -22078,7 +22078,7 @@
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD125" t="inlineStr">
@@ -22113,17 +22113,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>New Zealand PHF Science monthly cryptosporidiosis notifications.</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN125" t="b">
@@ -22146,7 +22146,7 @@
       </c>
       <c r="AS125" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+          <t>SER_NZ_CRYPTOSPORIDIOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT125" t="n">
@@ -22159,42 +22159,42 @@
       </c>
       <c r="AV125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA125" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB125" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC125" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -22226,12 +22226,12 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -22256,7 +22256,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
@@ -22265,81 +22265,95 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>0.5887274669818509</v>
       </c>
       <c r="S126" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS126" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ126" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS126" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22366,17 +22380,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -22401,7 +22415,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -22410,81 +22424,170 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="O127" t="n">
-        <v>91</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.0260718470082014</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Cryptosporidiuminfektion</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS127" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ127" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS127" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
+        </is>
+      </c>
       <c r="AT127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -22546,7 +22649,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -22691,7 +22794,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -22700,13 +22803,13 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="O129" t="n">
-        <v>157</v>
+        <v>91</v>
       </c>
       <c r="R129" t="n">
-        <v>0.04498109868447935</v>
+        <v>0.0260718470082014</v>
       </c>
       <c r="S129" t="inlineStr">
         <is>
@@ -22836,7 +22939,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
@@ -22981,7 +23084,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
@@ -22990,13 +23093,13 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
       <c r="O131" t="n">
-        <v>216</v>
+        <v>157</v>
       </c>
       <c r="R131" t="n">
-        <v>0.06188482366781873</v>
+        <v>0.04498109868447935</v>
       </c>
       <c r="S131" t="inlineStr">
         <is>
@@ -23126,7 +23229,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -23271,7 +23374,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
@@ -23280,13 +23383,13 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="O133" t="n">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="R133" t="n">
-        <v>0.0647498618005881</v>
+        <v>0.06188482366781873</v>
       </c>
       <c r="S133" t="inlineStr">
         <is>
@@ -23416,7 +23519,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
@@ -23531,12 +23634,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -23561,22 +23664,22 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N135" t="n">
-        <v>101</v>
+        <v>226</v>
       </c>
       <c r="O135" t="n">
-        <v>101</v>
+        <v>226</v>
       </c>
       <c r="R135" t="n">
-        <v>0.3709539937714988</v>
+        <v>0.0647498618005881</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -23609,42 +23712,42 @@
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -23676,12 +23779,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -23706,104 +23809,90 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N136" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="R136" t="n">
-        <v>0.8360403103061447</v>
+        <v>0</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AA136" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ136" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS136" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR136" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -23830,17 +23919,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -23874,170 +23963,81 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>47</v>
+        <v>109</v>
       </c>
       <c r="O137" t="n">
-        <v>47</v>
-      </c>
-      <c r="U137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="V137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="W137" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X137" t="inlineStr">
-        <is>
-          <t>Cryptosporidiosis</t>
-        </is>
-      </c>
-      <c r="Y137" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z137" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA137" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB137" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD137" t="inlineStr">
+        <v>109</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.4003364883276571</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr"/>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE137" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF137" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG137" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH137" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK137" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
-        </is>
-      </c>
-      <c r="AM137" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN137" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP137" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ137" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS137" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1270</t>
-        </is>
-      </c>
-      <c r="AT137" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV137" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -24069,12 +24069,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -24108,13 +24108,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="O138" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="R138" t="n">
-        <v>1.185213803282989</v>
+        <v>0.9783450439752756</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -24143,12 +24143,12 @@
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -24156,47 +24156,47 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24228,12 +24228,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -24267,29 +24267,29 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="O139" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Cryptosporidose</t>
+          <t>Cryptosporidiosis</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -24314,7 +24314,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -24349,17 +24349,17 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 1270.</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -24377,12 +24377,12 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_309_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -24390,47 +24390,47 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24462,12 +24462,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -24501,81 +24501,95 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>229</v>
+        <v>113</v>
       </c>
       <c r="O140" t="n">
-        <v>229</v>
+        <v>113</v>
       </c>
       <c r="R140" t="n">
-        <v>0.06560937324041893</v>
+        <v>1.998942683148922</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24602,17 +24616,17 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -24637,7 +24651,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -24646,81 +24660,170 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
-      </c>
-      <c r="R141" t="n">
-        <v>0</v>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>113</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Cryptosporidose</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>1</v>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_309_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -24782,7 +24885,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M142" t="inlineStr">
@@ -24791,13 +24894,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="O142" t="n">
-        <v>187</v>
+        <v>229</v>
       </c>
       <c r="R142" t="n">
-        <v>0.0535762130827875</v>
+        <v>0.06560937324041893</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -24927,7 +25030,7 @@
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -25072,7 +25175,7 @@
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
@@ -25081,13 +25184,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="O144" t="n">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="R144" t="n">
-        <v>0.05558173977572607</v>
+        <v>0.0535762130827875</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -25156,6 +25259,441 @@
       <c r="BC144" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" t="n">
+        <v>0</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr"/>
+      <c r="AT145" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>194</v>
+      </c>
+      <c r="O146" t="n">
+        <v>194</v>
+      </c>
+      <c r="R146" t="n">
+        <v>0.05558173977572607</v>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr"/>
+      <c r="AT146" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="O147" t="n">
+        <v>0</v>
+      </c>
+      <c r="R147" t="n">
+        <v>0</v>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
+      <c r="AT147" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -25192,7 +25730,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -25275,7 +25813,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -25285,7 +25823,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -25305,7 +25843,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -25337,7 +25875,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6101</v>
+        <v>6192</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23963,13 +23963,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="O137" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="R137" t="n">
-        <v>0.4003364883276571</v>
+        <v>0.4223733592447758</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6192</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -24108,13 +24108,13 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O138" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="R138" t="n">
-        <v>0.9783450439752756</v>
+        <v>1.049497410809841</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -24267,10 +24267,10 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="O139" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
@@ -25694,6 +25694,151 @@
       <c r="BC147" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D096</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Cryptosporidiosis</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>隐孢子虫病</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>212</v>
+      </c>
+      <c r="O148" t="n">
+        <v>212</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.06073880841471097</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr"/>
+      <c r="AT148" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25875,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -25813,7 +25958,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10">
@@ -25823,7 +25968,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -25875,7 +26020,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6198</v>
+        <v>6414</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -23963,13 +23963,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="O137" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="R137" t="n">
-        <v>0.4223733592447758</v>
+        <v>0.4517558538009342</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6414</v>
+        <v>6422</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -1336,17 +1336,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -1562,7 +1567,7 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1570,17 +1575,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
@@ -1721,7 +1731,7 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -1729,17 +1739,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
@@ -1955,7 +1970,7 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -1963,17 +1978,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
@@ -2510,7 +2530,7 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -2518,17 +2538,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS11" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
@@ -2744,7 +2769,7 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -2752,17 +2777,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS12" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
@@ -4773,7 +4803,7 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
@@ -4781,17 +4811,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS25" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
@@ -5007,7 +5042,7 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
@@ -5015,17 +5050,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS26" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
@@ -5166,7 +5206,7 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
@@ -5174,17 +5214,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS27" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
@@ -5400,7 +5445,7 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
@@ -5408,17 +5453,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS28" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
@@ -5955,7 +6005,7 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
@@ -5963,17 +6013,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS31" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
@@ -6189,7 +6244,7 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
@@ -6197,17 +6252,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS32" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
@@ -8070,7 +8130,7 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
@@ -8078,17 +8138,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS44" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
@@ -8304,7 +8369,7 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
@@ -8312,17 +8377,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS45" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
@@ -8463,7 +8533,7 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
@@ -8471,17 +8541,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS46" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
@@ -8697,7 +8772,7 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
@@ -8705,17 +8780,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS47" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
@@ -9252,7 +9332,7 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
@@ -9260,17 +9340,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS50" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
@@ -9486,7 +9571,7 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
@@ -9494,17 +9579,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS51" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
@@ -11364,7 +11454,7 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ63" t="inlineStr">
@@ -11372,17 +11462,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS63" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU63" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV63" t="inlineStr">
@@ -11598,7 +11693,7 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ64" t="inlineStr">
@@ -11606,17 +11701,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS64" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU64" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV64" t="inlineStr">
@@ -11757,7 +11857,7 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ65" t="inlineStr">
@@ -11765,17 +11865,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS65" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV65" t="inlineStr">
@@ -11991,7 +12096,7 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ66" t="inlineStr">
@@ -11999,17 +12104,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS66" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV66" t="inlineStr">
@@ -12543,7 +12653,7 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ69" t="inlineStr">
@@ -12551,17 +12661,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS69" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU69" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV69" t="inlineStr">
@@ -12777,7 +12892,7 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ70" t="inlineStr">
@@ -12785,17 +12900,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS70" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU70" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV70" t="inlineStr">
@@ -14655,7 +14775,7 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
@@ -14663,17 +14783,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR82" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS82" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
@@ -14889,7 +15014,7 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ83" t="inlineStr">
@@ -14897,17 +15022,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS83" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
@@ -15048,7 +15178,7 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ84" t="inlineStr">
@@ -15056,17 +15186,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR84" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS84" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV84" t="inlineStr">
@@ -15282,7 +15417,7 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ85" t="inlineStr">
@@ -15290,17 +15425,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS85" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
@@ -15834,7 +15974,7 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
@@ -15842,17 +15982,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS88" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
@@ -16068,7 +16213,7 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
@@ -16076,17 +16221,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR89" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS89" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
@@ -18239,7 +18389,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -18247,17 +18397,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS103" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
@@ -18473,7 +18628,7 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
@@ -18481,17 +18636,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS104" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
@@ -18632,7 +18792,7 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ105" t="inlineStr">
@@ -18640,17 +18800,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS105" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU105" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV105" t="inlineStr">
@@ -18866,7 +19031,7 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ106" t="inlineStr">
@@ -18874,17 +19039,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR106" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS106" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU106" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV106" t="inlineStr">
@@ -19418,7 +19588,7 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
@@ -19426,17 +19596,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR109" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS109" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
@@ -19652,7 +19827,7 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
@@ -19660,17 +19835,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR110" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS110" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
@@ -21116,7 +21296,7 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
@@ -21124,17 +21304,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR120" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS120" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
@@ -21350,7 +21535,7 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ121" t="inlineStr">
@@ -21358,17 +21543,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR121" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS121" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU121" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV121" t="inlineStr">
@@ -21509,7 +21699,7 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ122" t="inlineStr">
@@ -21517,17 +21707,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR122" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS122" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU122" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV122" t="inlineStr">
@@ -21743,7 +21938,7 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ123" t="inlineStr">
@@ -21751,17 +21946,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR123" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS123" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU123" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV123" t="inlineStr">
@@ -22295,7 +22495,7 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
@@ -22303,17 +22503,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR126" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS126" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
@@ -22529,7 +22734,7 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
@@ -22537,17 +22742,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR127" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS127" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_CRYPTOSPORIDIUM</t>
         </is>
       </c>
       <c r="AT127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
@@ -23963,13 +24173,13 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="O137" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="R137" t="n">
-        <v>0.4517558538009342</v>
+        <v>0.4701199128985332</v>
       </c>
       <c r="S137" t="inlineStr">
         <is>
@@ -24138,7 +24348,7 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ138" t="inlineStr">
@@ -24146,17 +24356,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS138" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
@@ -24372,7 +24587,7 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
@@ -24380,17 +24595,22 @@
           <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS139" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1270</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
@@ -24531,7 +24751,7 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ140" t="inlineStr">
@@ -24539,17 +24759,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS140" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
@@ -24765,7 +24990,7 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
@@ -24773,17 +24998,22 @@
           <t>parity</t>
         </is>
       </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
       <c r="AS141" t="inlineStr">
         <is>
           <t>SER_NO_FHI_309_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
@@ -26020,7 +26250,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6422</v>
+        <v>6427</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d096/2026-2029.xlsx
+++ b/diseases/d096/2026-2029.xlsx
@@ -25877,13 +25877,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O149" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="R149" t="n">
-        <v>0.52521209019133</v>
+        <v>0.5325577138303695</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -29127,13 +29127,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R170" t="n">
-        <v>0</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -29272,13 +29272,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R171" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -29436,10 +29436,10 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O172" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -30189,7 +30189,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7060</v>
+        <v>7067</v>
       </c>
     </row>
     <row r="16">
